--- a/site/leagues/proliga/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_GCO.xlsx
+++ b/site/leagues/proliga/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_GCO.xlsx
@@ -1185,13 +1185,13 @@
         <v>82</v>
       </c>
       <c r="C2" t="n">
-        <v>76.09999999999999</v>
+        <v>76.3</v>
       </c>
       <c r="D2" t="n">
         <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="3">
@@ -1204,13 +1204,13 @@
         <v>97.59999999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>97.8</v>
+        <v>97.3</v>
       </c>
       <c r="D3" t="n">
         <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="4">
@@ -1223,13 +1223,13 @@
         <v>116.4</v>
       </c>
       <c r="C4" t="n">
-        <v>97.90000000000001</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="D4" t="n">
         <v>16</v>
       </c>
       <c r="E4" t="n">
-        <v>18.5</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="5">
@@ -1242,13 +1242,13 @@
         <v>-18.7</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D5" t="n">
         <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>-18.7</v>
+        <v>-19</v>
       </c>
     </row>
     <row r="6">
@@ -1261,7 +1261,7 @@
         <v>13.7</v>
       </c>
       <c r="C6" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="D6" t="n">
         <v>8</v>
@@ -1318,13 +1318,13 @@
         <v>20.7</v>
       </c>
       <c r="C9" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="D9" t="n">
         <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
